--- a/GOLDEN_DATASET/data/cached_scores/sample_dataset_cached_scores.xlsx
+++ b/GOLDEN_DATASET/data/cached_scores/sample_dataset_cached_scores.xlsx
@@ -455,7 +455,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C2" t="n">
         <v>0.5625</v>
@@ -469,7 +469,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C3" t="n">
         <v>0.51171875</v>
@@ -483,7 +483,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C4" t="n">
         <v>0.5559895833333334</v>
@@ -497,7 +497,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.4800000000000001</v>
       </c>
       <c r="C5" t="n">
         <v>0.559765625</v>
@@ -511,7 +511,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C6" t="n">
         <v>0.5286458333333334</v>
@@ -525,7 +525,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="C7" t="n">
         <v>0.5234375</v>
@@ -539,7 +539,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="n">
         <v>0.53515625</v>
@@ -553,7 +553,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.6888888888888888</v>
       </c>
       <c r="C9" t="n">
         <v>0.513671875</v>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="C10" t="n">
         <v>0.525390625</v>
@@ -581,7 +581,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.4555555555555555</v>
       </c>
       <c r="C11" t="n">
         <v>0.5126953125</v>
@@ -595,7 +595,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C12" t="n">
         <v>0.4986979166666667</v>
@@ -609,7 +609,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="C13" t="n">
         <v>0.4931640625</v>
@@ -623,7 +623,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C14" t="n">
         <v>0.56982421875</v>
@@ -637,7 +637,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C15" t="n">
         <v>0.4990234375</v>
@@ -651,7 +651,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C16" t="n">
         <v>0.505859375</v>
@@ -665,7 +665,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C17" t="n">
         <v>0.4921875</v>
@@ -679,7 +679,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="C18" t="n">
         <v>0.52587890625</v>
@@ -693,7 +693,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="C19" t="n">
         <v>0.49365234375</v>
@@ -707,7 +707,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="C20" t="n">
         <v>0.471875</v>
@@ -721,7 +721,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C21" t="n">
         <v>0.505859375</v>
@@ -735,7 +735,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>0.6888888888888888</v>
       </c>
       <c r="C22" t="n">
         <v>0.4654947916666667</v>
@@ -749,7 +749,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C23" t="n">
         <v>0.498046875</v>
@@ -763,7 +763,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.6888888888888888</v>
       </c>
       <c r="C24" t="n">
         <v>0.5423177083333334</v>
@@ -777,7 +777,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C25" t="n">
         <v>0.4869791666666667</v>
@@ -791,7 +791,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C26" t="n">
         <v>0.5345052083333334</v>
@@ -805,7 +805,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C27" t="n">
         <v>0.5234375</v>
@@ -819,7 +819,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="C28" t="n">
         <v>0.5266927083333334</v>
@@ -833,7 +833,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="C29" t="n">
         <v>0.4739583333333333</v>
@@ -847,7 +847,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.3444444444444445</v>
       </c>
       <c r="C30" t="n">
         <v>0.4869791666666667</v>
@@ -861,7 +861,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C31" t="n">
         <v>0.5009765625</v>
@@ -875,7 +875,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C32" t="n">
         <v>0.50830078125</v>
@@ -889,7 +889,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C33" t="n">
         <v>0.50244140625</v>
@@ -903,7 +903,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C34" t="n">
         <v>0.50048828125</v>
@@ -917,7 +917,7 @@
         <v>37</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C35" t="n">
         <v>0.447265625</v>
@@ -931,7 +931,7 @@
         <v>38</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C36" t="n">
         <v>0.4875</v>
@@ -945,7 +945,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C37" t="n">
         <v>0.4401041666666667</v>
@@ -959,7 +959,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C38" t="n">
         <v>0.4794921875</v>
@@ -973,7 +973,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C39" t="n">
         <v>0.4309895833333333</v>
@@ -987,7 +987,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C40" t="n">
         <v>0.439453125</v>
@@ -1001,7 +1001,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="C41" t="n">
         <v>0.435546875</v>
@@ -1015,7 +1015,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C42" t="n">
         <v>0.431640625</v>
@@ -1029,7 +1029,7 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="C43" t="n">
         <v>0.42138671875</v>
@@ -1043,7 +1043,7 @@
         <v>49</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="C44" t="n">
         <v>0.54296875</v>
@@ -1057,7 +1057,7 @@
         <v>50</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C45" t="n">
         <v>0.47265625</v>
@@ -1071,7 +1071,7 @@
         <v>54</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C46" t="n">
         <v>0.41015625</v>
@@ -1085,7 +1085,7 @@
         <v>55</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C47" t="n">
         <v>0.4029947916666667</v>
@@ -1099,7 +1099,7 @@
         <v>56</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C48" t="n">
         <v>0.41796875</v>
@@ -1113,7 +1113,7 @@
         <v>58</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="C49" t="n">
         <v>0.4778645833333333</v>
@@ -1127,7 +1127,7 @@
         <v>59</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C50" t="n">
         <v>0.419921875</v>
@@ -1141,7 +1141,7 @@
         <v>62</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>0.4533333333333333</v>
       </c>
       <c r="C51" t="n">
         <v>0.4640625</v>
@@ -1155,7 +1155,7 @@
         <v>63</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="C52" t="n">
         <v>0.5810546875</v>
@@ -1169,7 +1169,7 @@
         <v>64</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>0.4133333333333333</v>
       </c>
       <c r="C53" t="n">
         <v>0.46171875</v>
@@ -1183,7 +1183,7 @@
         <v>65</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C54" t="n">
         <v>0.416015625</v>
@@ -1197,7 +1197,7 @@
         <v>66</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C55" t="n">
         <v>0.4189453125</v>
@@ -1211,7 +1211,7 @@
         <v>67</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C56" t="n">
         <v>0.40185546875</v>
@@ -1225,7 +1225,7 @@
         <v>68</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>0.4833333333333334</v>
       </c>
       <c r="C57" t="n">
         <v>0.3974609375</v>
@@ -1239,7 +1239,7 @@
         <v>69</v>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C58" t="n">
         <v>0.380859375</v>
@@ -1253,7 +1253,7 @@
         <v>70</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="C59" t="n">
         <v>0.5263671875</v>
@@ -1267,7 +1267,7 @@
         <v>71</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>0.3904761904761904</v>
       </c>
       <c r="C60" t="n">
         <v>0.4347098214285715</v>
@@ -1281,7 +1281,7 @@
         <v>72</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="C61" t="n">
         <v>0.3854166666666667</v>
@@ -1295,7 +1295,7 @@
         <v>73</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C62" t="n">
         <v>0.4013671875</v>
@@ -1309,7 +1309,7 @@
         <v>74</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C63" t="n">
         <v>0.4345703125</v>
@@ -1323,7 +1323,7 @@
         <v>75</v>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C64" t="n">
         <v>0.423828125</v>
@@ -1337,7 +1337,7 @@
         <v>76</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C65" t="n">
         <v>0.4231770833333333</v>
@@ -1351,7 +1351,7 @@
         <v>77</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="C66" t="n">
         <v>0.4654947916666667</v>
@@ -1365,7 +1365,7 @@
         <v>78</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C67" t="n">
         <v>0.5166015625</v>
@@ -1379,7 +1379,7 @@
         <v>79</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C68" t="n">
         <v>0.46484375</v>
@@ -1393,7 +1393,7 @@
         <v>80</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="C69" t="n">
         <v>0.44140625</v>
@@ -1407,7 +1407,7 @@
         <v>82</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C70" t="n">
         <v>0.3938802083333333</v>
@@ -1421,7 +1421,7 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C71" t="n">
         <v>0.3896484375</v>
@@ -1435,7 +1435,7 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C72" t="n">
         <v>0.41015625</v>
@@ -1449,7 +1449,7 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C73" t="n">
         <v>0.46484375</v>
@@ -1463,7 +1463,7 @@
         <v>86</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C74" t="n">
         <v>0.4677734375</v>
@@ -1477,7 +1477,7 @@
         <v>87</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="C75" t="n">
         <v>0.50390625</v>
@@ -1491,7 +1491,7 @@
         <v>88</v>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C76" t="n">
         <v>0.4990234375</v>
@@ -1505,7 +1505,7 @@
         <v>89</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C77" t="n">
         <v>0.46484375</v>
@@ -1519,7 +1519,7 @@
         <v>90</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="C78" t="n">
         <v>0.4036458333333333</v>
@@ -1533,7 +1533,7 @@
         <v>91</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C79" t="n">
         <v>0.36328125</v>
@@ -1547,7 +1547,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="C80" t="n">
         <v>0.5690104166666666</v>
@@ -1561,7 +1561,7 @@
         <v>93</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="C81" t="n">
         <v>0.3704427083333333</v>
@@ -1575,7 +1575,7 @@
         <v>94</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C82" t="n">
         <v>0.34375</v>
@@ -1589,7 +1589,7 @@
         <v>95</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C83" t="n">
         <v>0.453125</v>
@@ -1603,7 +1603,7 @@
         <v>96</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C84" t="n">
         <v>0.4521484375</v>
@@ -1617,7 +1617,7 @@
         <v>98</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C85" t="n">
         <v>0.490234375</v>
@@ -1631,7 +1631,7 @@
         <v>99</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C86" t="n">
         <v>0.4501953125</v>
@@ -1645,7 +1645,7 @@
         <v>100</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="C87" t="n">
         <v>0.48671875</v>
@@ -1659,7 +1659,7 @@
         <v>101</v>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C88" t="n">
         <v>0.55078125</v>
@@ -1673,7 +1673,7 @@
         <v>102</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C89" t="n">
         <v>0.443359375</v>
@@ -1687,7 +1687,7 @@
         <v>103</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C90" t="n">
         <v>0.4384765625</v>
@@ -1701,7 +1701,7 @@
         <v>104</v>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C91" t="n">
         <v>0.4892578125</v>
@@ -1715,7 +1715,7 @@
         <v>105</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="C92" t="n">
         <v>0.4765625</v>
@@ -1729,7 +1729,7 @@
         <v>107</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C93" t="n">
         <v>0.56689453125</v>
@@ -1743,7 +1743,7 @@
         <v>108</v>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C94" t="n">
         <v>0.4856770833333333</v>
@@ -1757,7 +1757,7 @@
         <v>109</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C95" t="n">
         <v>0.5361328125</v>
@@ -1771,7 +1771,7 @@
         <v>110</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C96" t="n">
         <v>0.341796875</v>
@@ -1785,7 +1785,7 @@
         <v>112</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C97" t="n">
         <v>0.455078125</v>
@@ -1799,7 +1799,7 @@
         <v>113</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C98" t="n">
         <v>0.3623046875</v>
@@ -1813,7 +1813,7 @@
         <v>114</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C99" t="n">
         <v>0.3623046875</v>
@@ -1827,7 +1827,7 @@
         <v>115</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C100" t="n">
         <v>0.427734375</v>
@@ -1841,7 +1841,7 @@
         <v>116</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>0.4190476190476191</v>
       </c>
       <c r="C101" t="n">
         <v>0.5159040178571429</v>
@@ -1855,7 +1855,7 @@
         <v>117</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="C102" t="n">
         <v>0.55908203125</v>
@@ -1869,7 +1869,7 @@
         <v>118</v>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C103" t="n">
         <v>0.4680989583333333</v>
@@ -1883,7 +1883,7 @@
         <v>119</v>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="C104" t="n">
         <v>0.43115234375</v>
@@ -1897,7 +1897,7 @@
         <v>120</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="C105" t="n">
         <v>0.4615885416666667</v>
@@ -1911,7 +1911,7 @@
         <v>122</v>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C106" t="n">
         <v>0.43505859375</v>
@@ -1925,7 +1925,7 @@
         <v>123</v>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C107" t="n">
         <v>0.44970703125</v>
@@ -1939,7 +1939,7 @@
         <v>124</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C108" t="n">
         <v>0.484375</v>
@@ -1953,7 +1953,7 @@
         <v>125</v>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="C109" t="n">
         <v>0.4837239583333333</v>
@@ -1967,7 +1967,7 @@
         <v>126</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C110" t="n">
         <v>0.3603515625</v>
@@ -1981,7 +1981,7 @@
         <v>127</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C111" t="n">
         <v>0.44921875</v>
@@ -1995,7 +1995,7 @@
         <v>128</v>
       </c>
       <c r="B112" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C112" t="n">
         <v>0.4446614583333333</v>
@@ -2009,7 +2009,7 @@
         <v>129</v>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>0.5333333333333334</v>
       </c>
       <c r="C113" t="n">
         <v>0.4833984375</v>
@@ -2023,7 +2023,7 @@
         <v>130</v>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="C114" t="n">
         <v>0.3600260416666667</v>
@@ -2037,7 +2037,7 @@
         <v>131</v>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="C115" t="n">
         <v>0.4671875</v>
@@ -2051,7 +2051,7 @@
         <v>132</v>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="C116" t="n">
         <v>0.4466145833333333</v>
@@ -2065,7 +2065,7 @@
         <v>133</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C117" t="n">
         <v>0.4329427083333333</v>
@@ -2079,7 +2079,7 @@
         <v>134</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="C118" t="n">
         <v>0.40966796875</v>
@@ -2093,7 +2093,7 @@
         <v>135</v>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C119" t="n">
         <v>0.4173177083333333</v>
@@ -2107,7 +2107,7 @@
         <v>136</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C120" t="n">
         <v>0.412109375</v>
@@ -2121,7 +2121,7 @@
         <v>137</v>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C121" t="n">
         <v>0.462890625</v>
@@ -2135,7 +2135,7 @@
         <v>138</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="C122" t="n">
         <v>0.404296875</v>
@@ -2149,7 +2149,7 @@
         <v>139</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="C123" t="n">
         <v>0.3984375</v>
@@ -2163,7 +2163,7 @@
         <v>140</v>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C124" t="n">
         <v>0.396484375</v>
@@ -2177,7 +2177,7 @@
         <v>141</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C125" t="n">
         <v>0.3938802083333333</v>
@@ -2191,7 +2191,7 @@
         <v>142</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C126" t="n">
         <v>0.392578125</v>
@@ -2205,7 +2205,7 @@
         <v>143</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C127" t="n">
         <v>0.3873697916666667</v>
@@ -2219,7 +2219,7 @@
         <v>144</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="C128" t="n">
         <v>0.3828125</v>
@@ -2233,7 +2233,7 @@
         <v>145</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="C129" t="n">
         <v>0.375</v>
@@ -2247,7 +2247,7 @@
         <v>146</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C130" t="n">
         <v>0.3684895833333333</v>
@@ -2261,7 +2261,7 @@
         <v>147</v>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="C131" t="n">
         <v>0.3365885416666667</v>
@@ -2275,7 +2275,7 @@
         <v>148</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="C132" t="n">
         <v>0.407421875</v>
@@ -2289,7 +2289,7 @@
         <v>149</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>0.4095238095238096</v>
       </c>
       <c r="C133" t="n">
         <v>0.423828125</v>
@@ -2303,7 +2303,7 @@
         <v>150</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C134" t="n">
         <v>0.3857421875</v>
@@ -2317,7 +2317,7 @@
         <v>151</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C135" t="n">
         <v>0.494140625</v>
@@ -2331,7 +2331,7 @@
         <v>152</v>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C136" t="n">
         <v>0.3818359375</v>
@@ -2345,7 +2345,7 @@
         <v>153</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C137" t="n">
         <v>0.48828125</v>
@@ -2359,7 +2359,7 @@
         <v>154</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>0.5333333333333334</v>
       </c>
       <c r="C138" t="n">
         <v>0.4828125</v>
@@ -2373,7 +2373,7 @@
         <v>155</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="C139" t="n">
         <v>0.3916015625</v>
@@ -2387,7 +2387,7 @@
         <v>156</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>0.4416666666666667</v>
       </c>
       <c r="C140" t="n">
         <v>0.44140625</v>
@@ -2401,7 +2401,7 @@
         <v>157</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>0.3185185185185185</v>
       </c>
       <c r="C141" t="n">
         <v>0.4136284722222222</v>
@@ -2415,7 +2415,7 @@
         <v>158</v>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C142" t="n">
         <v>0.4524739583333333</v>
@@ -2429,7 +2429,7 @@
         <v>159</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>0.4733333333333333</v>
       </c>
       <c r="C143" t="n">
         <v>0.426171875</v>
@@ -2443,7 +2443,7 @@
         <v>160</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C144" t="n">
         <v>0.3697916666666667</v>
@@ -2457,7 +2457,7 @@
         <v>161</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C145" t="n">
         <v>0.4150390625</v>
@@ -2471,7 +2471,7 @@
         <v>162</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C146" t="n">
         <v>0.411376953125</v>
@@ -2485,7 +2485,7 @@
         <v>163</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C147" t="n">
         <v>0.3681640625</v>
@@ -2499,7 +2499,7 @@
         <v>164</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C148" t="n">
         <v>0.359375</v>
@@ -2513,7 +2513,7 @@
         <v>165</v>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="C149" t="n">
         <v>0.3118489583333333</v>
@@ -2527,7 +2527,7 @@
         <v>166</v>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C150" t="n">
         <v>0.36328125</v>
@@ -2541,7 +2541,7 @@
         <v>167</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C151" t="n">
         <v>0.408203125</v>
@@ -2555,7 +2555,7 @@
         <v>168</v>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="C152" t="n">
         <v>0.3798828125</v>
@@ -2569,7 +2569,7 @@
         <v>169</v>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>0.3833333333333333</v>
       </c>
       <c r="C153" t="n">
         <v>0.39990234375</v>
@@ -2583,7 +2583,7 @@
         <v>170</v>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="C154" t="n">
         <v>0.39599609375</v>
@@ -2597,7 +2597,7 @@
         <v>171</v>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C155" t="n">
         <v>0.365234375</v>
@@ -2611,7 +2611,7 @@
         <v>172</v>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="C156" t="n">
         <v>0.3623046875</v>
@@ -2625,7 +2625,7 @@
         <v>174</v>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="C157" t="n">
         <v>0.4173177083333333</v>
@@ -2639,7 +2639,7 @@
         <v>175</v>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C158" t="n">
         <v>0.3528645833333333</v>
@@ -2653,7 +2653,7 @@
         <v>176</v>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C159" t="n">
         <v>0.3411458333333333</v>
@@ -2667,7 +2667,7 @@
         <v>177</v>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>0.2916666666666666</v>
       </c>
       <c r="C160" t="n">
         <v>0.38916015625</v>
@@ -2681,7 +2681,7 @@
         <v>179</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C161" t="n">
         <v>0.3938802083333333</v>
@@ -2695,7 +2695,7 @@
         <v>180</v>
       </c>
       <c r="B162" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C162" t="n">
         <v>0.345703125</v>
@@ -2709,7 +2709,7 @@
         <v>181</v>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C163" t="n">
         <v>0.3828125</v>
@@ -2723,7 +2723,7 @@
         <v>182</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C164" t="n">
         <v>0.3525390625</v>
@@ -2737,7 +2737,7 @@
         <v>183</v>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="C165" t="n">
         <v>0.3740234375</v>
@@ -2751,7 +2751,7 @@
         <v>184</v>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C166" t="n">
         <v>0.3404947916666667</v>
@@ -2765,7 +2765,7 @@
         <v>185</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C167" t="n">
         <v>0.3821614583333333</v>
@@ -2779,7 +2779,7 @@
         <v>186</v>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C168" t="n">
         <v>0.330078125</v>
@@ -2793,7 +2793,7 @@
         <v>187</v>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C169" t="n">
         <v>0.38525390625</v>
@@ -2807,7 +2807,7 @@
         <v>188</v>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C170" t="n">
         <v>0.4368489583333333</v>
@@ -2821,7 +2821,7 @@
         <v>189</v>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>0.5166666666666667</v>
       </c>
       <c r="C171" t="n">
         <v>0.353515625</v>
@@ -2835,7 +2835,7 @@
         <v>190</v>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C172" t="n">
         <v>0.359375</v>
@@ -2849,7 +2849,7 @@
         <v>191</v>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C173" t="n">
         <v>0.3782552083333333</v>
@@ -2863,7 +2863,7 @@
         <v>192</v>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C174" t="n">
         <v>0.3837890625</v>
@@ -2877,7 +2877,7 @@
         <v>193</v>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C175" t="n">
         <v>0.37841796875</v>
@@ -2891,7 +2891,7 @@
         <v>194</v>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C176" t="n">
         <v>0.3776041666666667</v>
@@ -2905,7 +2905,7 @@
         <v>195</v>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C177" t="n">
         <v>0.3987630208333333</v>
@@ -2919,7 +2919,7 @@
         <v>196</v>
       </c>
       <c r="B178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C178" t="n">
         <v>0.23828125</v>
@@ -2933,7 +2933,7 @@
         <v>197</v>
       </c>
       <c r="B179" t="n">
-        <v>0</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="C179" t="n">
         <v>0.4147135416666667</v>
@@ -2947,7 +2947,7 @@
         <v>198</v>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C180" t="n">
         <v>0.431640625</v>
@@ -2961,7 +2961,7 @@
         <v>199</v>
       </c>
       <c r="B181" t="n">
-        <v>0</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C181" t="n">
         <v>0.3912760416666667</v>
@@ -2975,7 +2975,7 @@
         <v>200</v>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C182" t="n">
         <v>0.4622395833333333</v>
@@ -2989,7 +2989,7 @@
         <v>201</v>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C183" t="n">
         <v>0.4111328125</v>
@@ -3003,7 +3003,7 @@
         <v>202</v>
       </c>
       <c r="B184" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C184" t="n">
         <v>0.4091796875</v>
@@ -3017,7 +3017,7 @@
         <v>203</v>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="C185" t="n">
         <v>0.3890625</v>
@@ -3031,7 +3031,7 @@
         <v>204</v>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C186" t="n">
         <v>0.2578125</v>
@@ -3045,7 +3045,7 @@
         <v>205</v>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C187" t="n">
         <v>0.3828125</v>
@@ -3059,7 +3059,7 @@
         <v>206</v>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C188" t="n">
         <v>0.3759765625</v>
@@ -3073,7 +3073,7 @@
         <v>207</v>
       </c>
       <c r="B189" t="n">
-        <v>0</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C189" t="n">
         <v>0.431640625</v>
@@ -3087,7 +3087,7 @@
         <v>208</v>
       </c>
       <c r="B190" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C190" t="n">
         <v>0.548828125</v>
@@ -3101,7 +3101,7 @@
         <v>209</v>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C191" t="n">
         <v>0.544921875</v>
@@ -3115,7 +3115,7 @@
         <v>210</v>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C192" t="n">
         <v>0.4697265625</v>
@@ -3129,7 +3129,7 @@
         <v>211</v>
       </c>
       <c r="B193" t="n">
-        <v>0</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="C193" t="n">
         <v>0.501953125</v>
@@ -3143,7 +3143,7 @@
         <v>212</v>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C194" t="n">
         <v>0.4889322916666667</v>
@@ -3157,7 +3157,7 @@
         <v>213</v>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C195" t="n">
         <v>0.53125</v>
@@ -3171,7 +3171,7 @@
         <v>214</v>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>0.8222222222222223</v>
       </c>
       <c r="C196" t="n">
         <v>0.4830729166666667</v>
@@ -3185,7 +3185,7 @@
         <v>215</v>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C197" t="n">
         <v>0.4609375</v>
@@ -3199,7 +3199,7 @@
         <v>216</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C198" t="n">
         <v>0.4736328125</v>
@@ -3213,7 +3213,7 @@
         <v>217</v>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C199" t="n">
         <v>0.458984375</v>
@@ -3227,7 +3227,7 @@
         <v>218</v>
       </c>
       <c r="B200" t="n">
-        <v>0</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="C200" t="n">
         <v>0.3912760416666667</v>
@@ -3241,7 +3241,7 @@
         <v>219</v>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C201" t="n">
         <v>0.4654947916666667</v>
@@ -3255,7 +3255,7 @@
         <v>220</v>
       </c>
       <c r="B202" t="n">
-        <v>0</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C202" t="n">
         <v>0.4622395833333333</v>
@@ -3269,7 +3269,7 @@
         <v>221</v>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C203" t="n">
         <v>0.4453125</v>
@@ -3283,7 +3283,7 @@
         <v>222</v>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C204" t="n">
         <v>0.462890625</v>
@@ -3297,7 +3297,7 @@
         <v>223</v>
       </c>
       <c r="B205" t="n">
-        <v>0</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C205" t="n">
         <v>0.4576822916666667</v>
@@ -3311,7 +3311,7 @@
         <v>224</v>
       </c>
       <c r="B206" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C206" t="n">
         <v>0.3897879464285715</v>
@@ -3325,7 +3325,7 @@
         <v>225</v>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="C207" t="n">
         <v>0.4505208333333333</v>
@@ -3339,7 +3339,7 @@
         <v>226</v>
       </c>
       <c r="B208" t="n">
-        <v>0</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C208" t="n">
         <v>0.4306640625</v>
@@ -3353,7 +3353,7 @@
         <v>227</v>
       </c>
       <c r="B209" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C209" t="n">
         <v>0.4296875</v>
@@ -3367,7 +3367,7 @@
         <v>228</v>
       </c>
       <c r="B210" t="n">
-        <v>0</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C210" t="n">
         <v>0.4010416666666667</v>
@@ -3381,7 +3381,7 @@
         <v>229</v>
       </c>
       <c r="B211" t="n">
-        <v>0</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C211" t="n">
         <v>0.443359375</v>
@@ -3395,7 +3395,7 @@
         <v>230</v>
       </c>
       <c r="B212" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C212" t="n">
         <v>0.4251302083333333</v>
@@ -3409,7 +3409,7 @@
         <v>232</v>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C213" t="n">
         <v>0.470703125</v>
@@ -3423,7 +3423,7 @@
         <v>234</v>
       </c>
       <c r="B214" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C214" t="n">
         <v>0.46875</v>
@@ -3437,7 +3437,7 @@
         <v>235</v>
       </c>
       <c r="B215" t="n">
-        <v>0</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="C215" t="n">
         <v>0.439453125</v>
@@ -3451,7 +3451,7 @@
         <v>236</v>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C216" t="n">
         <v>0.4912109375</v>
@@ -3465,7 +3465,7 @@
         <v>237</v>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C217" t="n">
         <v>0.48046875</v>
@@ -3479,7 +3479,7 @@
         <v>239</v>
       </c>
       <c r="B218" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C218" t="n">
         <v>0.4794921875</v>
@@ -3493,7 +3493,7 @@
         <v>240</v>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C219" t="n">
         <v>0.412109375</v>
@@ -3507,7 +3507,7 @@
         <v>241</v>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C220" t="n">
         <v>0.462890625</v>
@@ -3521,7 +3521,7 @@
         <v>243</v>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C221" t="n">
         <v>0.41015625</v>
@@ -3535,7 +3535,7 @@
         <v>244</v>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C222" t="n">
         <v>0.3854166666666667</v>
@@ -3549,7 +3549,7 @@
         <v>245</v>
       </c>
       <c r="B223" t="n">
-        <v>0</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="C223" t="n">
         <v>0.395703125</v>
@@ -3563,7 +3563,7 @@
         <v>246</v>
       </c>
       <c r="B224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C224" t="n">
         <v>0.3935546875</v>
@@ -3577,7 +3577,7 @@
         <v>247</v>
       </c>
       <c r="B225" t="n">
-        <v>0</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C225" t="n">
         <v>0.4153645833333333</v>
@@ -3591,7 +3591,7 @@
         <v>248</v>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="C226" t="n">
         <v>0.3624441964285715</v>
@@ -3605,7 +3605,7 @@
         <v>249</v>
       </c>
       <c r="B227" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C227" t="n">
         <v>0.2578125</v>
@@ -3619,7 +3619,7 @@
         <v>250</v>
       </c>
       <c r="B228" t="n">
-        <v>0</v>
+        <v>0.3538461538461539</v>
       </c>
       <c r="C228" t="n">
         <v>0.3533653846153846</v>
@@ -3633,7 +3633,7 @@
         <v>251</v>
       </c>
       <c r="B229" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C229" t="n">
         <v>0.451171875</v>
@@ -3647,7 +3647,7 @@
         <v>252</v>
       </c>
       <c r="B230" t="n">
-        <v>0</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="C230" t="n">
         <v>0.3665364583333333</v>
@@ -3661,7 +3661,7 @@
         <v>253</v>
       </c>
       <c r="B231" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="C231" t="n">
         <v>0.348046875</v>
@@ -3675,7 +3675,7 @@
         <v>254</v>
       </c>
       <c r="B232" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C232" t="n">
         <v>0.3701171875</v>
@@ -3689,7 +3689,7 @@
         <v>255</v>
       </c>
       <c r="B233" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C233" t="n">
         <v>0.35107421875</v>
@@ -3703,7 +3703,7 @@
         <v>256</v>
       </c>
       <c r="B234" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C234" t="n">
         <v>0.3935546875</v>
@@ -3717,7 +3717,7 @@
         <v>257</v>
       </c>
       <c r="B235" t="n">
-        <v>0</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="C235" t="n">
         <v>0.4108072916666667</v>
@@ -3731,7 +3731,7 @@
         <v>258</v>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="C236" t="n">
         <v>0.363525390625</v>
@@ -3745,7 +3745,7 @@
         <v>259</v>
       </c>
       <c r="B237" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C237" t="n">
         <v>0.34619140625</v>
@@ -3759,7 +3759,7 @@
         <v>260</v>
       </c>
       <c r="B238" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C238" t="n">
         <v>0.357421875</v>
@@ -3773,7 +3773,7 @@
         <v>261</v>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C239" t="n">
         <v>0.375</v>
@@ -3787,7 +3787,7 @@
         <v>262</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C240" t="n">
         <v>0.435546875</v>
@@ -3801,7 +3801,7 @@
         <v>263</v>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C241" t="n">
         <v>0.43359375</v>
@@ -3815,7 +3815,7 @@
         <v>264</v>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="C242" t="n">
         <v>0.3474609375</v>
@@ -3829,7 +3829,7 @@
         <v>265</v>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="C243" t="n">
         <v>0.427734375</v>
@@ -3843,7 +3843,7 @@
         <v>266</v>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>0.4133333333333334</v>
       </c>
       <c r="C244" t="n">
         <v>0.454296875</v>
@@ -3857,7 +3857,7 @@
         <v>267</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C245" t="n">
         <v>0.40625</v>
@@ -3871,7 +3871,7 @@
         <v>268</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C246" t="n">
         <v>0.42138671875</v>
@@ -3885,7 +3885,7 @@
         <v>269</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="C247" t="n">
         <v>0.419921875</v>
@@ -3899,7 +3899,7 @@
         <v>270</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C248" t="n">
         <v>0.4169921875</v>
@@ -3913,7 +3913,7 @@
         <v>271</v>
       </c>
       <c r="B249" t="n">
-        <v>0</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C249" t="n">
         <v>0.447265625</v>
@@ -3927,7 +3927,7 @@
         <v>272</v>
       </c>
       <c r="B250" t="n">
-        <v>0</v>
+        <v>0.5066666666666667</v>
       </c>
       <c r="C250" t="n">
         <v>0.429296875</v>
@@ -3941,7 +3941,7 @@
         <v>273</v>
       </c>
       <c r="B251" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C251" t="n">
         <v>0.41015625</v>
@@ -3955,7 +3955,7 @@
         <v>274</v>
       </c>
       <c r="B252" t="n">
-        <v>0</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C252" t="n">
         <v>0.4072265625</v>
@@ -3969,7 +3969,7 @@
         <v>275</v>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="C253" t="n">
         <v>0.39306640625</v>
@@ -3983,7 +3983,7 @@
         <v>276</v>
       </c>
       <c r="B254" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C254" t="n">
         <v>0.40625</v>
@@ -3997,7 +3997,7 @@
         <v>277</v>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C255" t="n">
         <v>0.41796875</v>
@@ -4011,7 +4011,7 @@
         <v>278</v>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C256" t="n">
         <v>0.359375</v>
@@ -4025,7 +4025,7 @@
         <v>279</v>
       </c>
       <c r="B257" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C257" t="n">
         <v>0.3815104166666667</v>
@@ -4039,7 +4039,7 @@
         <v>280</v>
       </c>
       <c r="B258" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C258" t="n">
         <v>0.34765625</v>
@@ -4053,7 +4053,7 @@
         <v>281</v>
       </c>
       <c r="B259" t="n">
-        <v>0</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="C259" t="n">
         <v>0.3447265625</v>
@@ -4067,7 +4067,7 @@
         <v>282</v>
       </c>
       <c r="B260" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C260" t="n">
         <v>0.4013671875</v>
@@ -4081,7 +4081,7 @@
         <v>283</v>
       </c>
       <c r="B261" t="n">
-        <v>0</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="C261" t="n">
         <v>0.3795572916666667</v>
@@ -4095,7 +4095,7 @@
         <v>284</v>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C262" t="n">
         <v>0.4915364583333333</v>
@@ -4109,7 +4109,7 @@
         <v>285</v>
       </c>
       <c r="B263" t="n">
-        <v>0</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C263" t="n">
         <v>0.3623046875</v>
@@ -4123,7 +4123,7 @@
         <v>286</v>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="C264" t="n">
         <v>0.423828125</v>
@@ -4137,7 +4137,7 @@
         <v>287</v>
       </c>
       <c r="B265" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C265" t="n">
         <v>0.353515625</v>
@@ -4151,7 +4151,7 @@
         <v>288</v>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C266" t="n">
         <v>0.4674479166666667</v>
@@ -4165,7 +4165,7 @@
         <v>289</v>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C267" t="n">
         <v>0.4814453125</v>
@@ -4179,7 +4179,7 @@
         <v>290</v>
       </c>
       <c r="B268" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C268" t="n">
         <v>0.392578125</v>
@@ -4193,7 +4193,7 @@
         <v>291</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C269" t="n">
         <v>0.44482421875</v>
@@ -4207,7 +4207,7 @@
         <v>292</v>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="C270" t="n">
         <v>0.3515625</v>
@@ -4221,7 +4221,7 @@
         <v>293</v>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C271" t="n">
         <v>0.380859375</v>
@@ -4235,7 +4235,7 @@
         <v>294</v>
       </c>
       <c r="B272" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C272" t="n">
         <v>0.36328125</v>
@@ -4249,7 +4249,7 @@
         <v>295</v>
       </c>
       <c r="B273" t="n">
-        <v>0</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C273" t="n">
         <v>0.4361979166666667</v>
@@ -4263,7 +4263,7 @@
         <v>296</v>
       </c>
       <c r="B274" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C274" t="n">
         <v>0.3515625</v>
@@ -4277,7 +4277,7 @@
         <v>297</v>
       </c>
       <c r="B275" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C275" t="n">
         <v>0.330078125</v>
@@ -4291,7 +4291,7 @@
         <v>298</v>
       </c>
       <c r="B276" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C276" t="n">
         <v>0.36328125</v>
@@ -4305,7 +4305,7 @@
         <v>299</v>
       </c>
       <c r="B277" t="n">
-        <v>0</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="C277" t="n">
         <v>0.3463541666666667</v>
@@ -4319,7 +4319,7 @@
         <v>300</v>
       </c>
       <c r="B278" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C278" t="n">
         <v>0.34375</v>
@@ -4333,7 +4333,7 @@
         <v>301</v>
       </c>
       <c r="B279" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C279" t="n">
         <v>0.3203125</v>
@@ -4347,7 +4347,7 @@
         <v>302</v>
       </c>
       <c r="B280" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C280" t="n">
         <v>0.3391927083333333</v>
@@ -4361,7 +4361,7 @@
         <v>303</v>
       </c>
       <c r="B281" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C281" t="n">
         <v>0.3326822916666667</v>
@@ -4375,7 +4375,7 @@
         <v>304</v>
       </c>
       <c r="B282" t="n">
-        <v>0</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="C282" t="n">
         <v>0.330078125</v>
@@ -4389,7 +4389,7 @@
         <v>305</v>
       </c>
       <c r="B283" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C283" t="n">
         <v>0.3743489583333333</v>
@@ -4403,7 +4403,7 @@
         <v>306</v>
       </c>
       <c r="B284" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C284" t="n">
         <v>0.3115234375</v>
@@ -4417,7 +4417,7 @@
         <v>307</v>
       </c>
       <c r="B285" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C285" t="n">
         <v>0.3203125</v>
@@ -4431,7 +4431,7 @@
         <v>308</v>
       </c>
       <c r="B286" t="n">
-        <v>0</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="C286" t="n">
         <v>0.4114583333333333</v>
@@ -4445,7 +4445,7 @@
         <v>309</v>
       </c>
       <c r="B287" t="n">
-        <v>0</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="C287" t="n">
         <v>0.310546875</v>
@@ -4459,7 +4459,7 @@
         <v>310</v>
       </c>
       <c r="B288" t="n">
-        <v>0</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="C288" t="n">
         <v>0.3899739583333333</v>
@@ -4473,7 +4473,7 @@
         <v>311</v>
       </c>
       <c r="B289" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C289" t="n">
         <v>0.37158203125</v>
@@ -4487,7 +4487,7 @@
         <v>312</v>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C290" t="n">
         <v>0.37109375</v>
@@ -4501,7 +4501,7 @@
         <v>313</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C291" t="n">
         <v>0.3352864583333333</v>
@@ -4515,7 +4515,7 @@
         <v>314</v>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C292" t="n">
         <v>0.4127604166666667</v>
@@ -4529,7 +4529,7 @@
         <v>315</v>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C293" t="n">
         <v>0.306640625</v>
@@ -4543,7 +4543,7 @@
         <v>316</v>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C294" t="n">
         <v>0.2887369791666667</v>
@@ -4557,7 +4557,7 @@
         <v>317</v>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C295" t="n">
         <v>0.3893229166666667</v>
@@ -4571,7 +4571,7 @@
         <v>318</v>
       </c>
       <c r="B296" t="n">
-        <v>0</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="C296" t="n">
         <v>0.2545572916666667</v>
@@ -4585,7 +4585,7 @@
         <v>319</v>
       </c>
       <c r="B297" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="C297" t="n">
         <v>0.2434895833333333</v>
@@ -4599,7 +4599,7 @@
         <v>320</v>
       </c>
       <c r="B298" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C298" t="n">
         <v>0.2825520833333333</v>
@@ -4613,7 +4613,7 @@
         <v>321</v>
       </c>
       <c r="B299" t="n">
-        <v>0</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="C299" t="n">
         <v>0.38671875</v>
@@ -4627,7 +4627,7 @@
         <v>322</v>
       </c>
       <c r="B300" t="n">
-        <v>0</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C300" t="n">
         <v>0.4205729166666667</v>
@@ -4641,7 +4641,7 @@
         <v>323</v>
       </c>
       <c r="B301" t="n">
-        <v>0</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C301" t="n">
         <v>0.37890625</v>
@@ -4655,7 +4655,7 @@
         <v>324</v>
       </c>
       <c r="B302" t="n">
-        <v>0</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C302" t="n">
         <v>0.3782552083333333</v>
@@ -4669,7 +4669,7 @@
         <v>325</v>
       </c>
       <c r="B303" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="C303" t="n">
         <v>0.365234375</v>
@@ -4683,7 +4683,7 @@
         <v>326</v>
       </c>
       <c r="B304" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C304" t="n">
         <v>0.3411458333333333</v>
@@ -4697,7 +4697,7 @@
         <v>327</v>
       </c>
       <c r="B305" t="n">
-        <v>0</v>
+        <v>0.6888888888888888</v>
       </c>
       <c r="C305" t="n">
         <v>0.333984375</v>
@@ -4711,7 +4711,7 @@
         <v>328</v>
       </c>
       <c r="B306" t="n">
-        <v>0</v>
+        <v>0.6888888888888888</v>
       </c>
       <c r="C306" t="n">
         <v>0.3274739583333333</v>
@@ -4725,7 +4725,7 @@
         <v>329</v>
       </c>
       <c r="B307" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C307" t="n">
         <v>0.33984375</v>
@@ -4739,7 +4739,7 @@
         <v>330</v>
       </c>
       <c r="B308" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C308" t="n">
         <v>0.3352864583333333</v>
@@ -4753,7 +4753,7 @@
         <v>331</v>
       </c>
       <c r="B309" t="n">
-        <v>0</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="C309" t="n">
         <v>0.3209635416666667</v>
@@ -4767,7 +4767,7 @@
         <v>332</v>
       </c>
       <c r="B310" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C310" t="n">
         <v>0.4462890625</v>
@@ -4781,7 +4781,7 @@
         <v>333</v>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C311" t="n">
         <v>0.404296875</v>
@@ -4795,7 +4795,7 @@
         <v>334</v>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="C312" t="n">
         <v>0.3899739583333333</v>
@@ -4809,7 +4809,7 @@
         <v>335</v>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C313" t="n">
         <v>0.380859375</v>
@@ -4823,7 +4823,7 @@
         <v>336</v>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C314" t="n">
         <v>0.373046875</v>
@@ -4837,7 +4837,7 @@
         <v>337</v>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C315" t="n">
         <v>0.3697916666666667</v>
@@ -4851,7 +4851,7 @@
         <v>338</v>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C316" t="n">
         <v>0.3606770833333333</v>
@@ -4865,7 +4865,7 @@
         <v>339</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C317" t="n">
         <v>0.357421875</v>
@@ -4879,7 +4879,7 @@
         <v>340</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C318" t="n">
         <v>0.353515625</v>
@@ -4893,7 +4893,7 @@
         <v>341</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C319" t="n">
         <v>0.349609375</v>
@@ -4907,7 +4907,7 @@
         <v>342</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C320" t="n">
         <v>0.3483072916666667</v>
@@ -4921,7 +4921,7 @@
         <v>343</v>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C321" t="n">
         <v>0.345703125</v>
@@ -4935,7 +4935,7 @@
         <v>344</v>
       </c>
       <c r="B322" t="n">
-        <v>0</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C322" t="n">
         <v>0.3450520833333333</v>
@@ -4949,7 +4949,7 @@
         <v>345</v>
       </c>
       <c r="B323" t="n">
-        <v>0</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C323" t="n">
         <v>0.33984375</v>
@@ -4963,7 +4963,7 @@
         <v>346</v>
       </c>
       <c r="B324" t="n">
-        <v>0</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C324" t="n">
         <v>0.337890625</v>
@@ -4977,7 +4977,7 @@
         <v>347</v>
       </c>
       <c r="B325" t="n">
-        <v>0</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C325" t="n">
         <v>0.337890625</v>
@@ -4991,7 +4991,7 @@
         <v>348</v>
       </c>
       <c r="B326" t="n">
-        <v>0</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C326" t="n">
         <v>0.3365885416666667</v>
@@ -5005,7 +5005,7 @@
         <v>349</v>
       </c>
       <c r="B327" t="n">
-        <v>0</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C327" t="n">
         <v>0.3346354166666667</v>
@@ -5019,7 +5019,7 @@
         <v>350</v>
       </c>
       <c r="B328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C328" t="n">
         <v>0.3326822916666667</v>
@@ -5033,7 +5033,7 @@
         <v>351</v>
       </c>
       <c r="B329" t="n">
-        <v>0</v>
+        <v>0.7111111111111112</v>
       </c>
       <c r="C329" t="n">
         <v>0.3294270833333333</v>
@@ -5047,7 +5047,7 @@
         <v>352</v>
       </c>
       <c r="B330" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C330" t="n">
         <v>0.3255208333333333</v>
@@ -5061,7 +5061,7 @@
         <v>353</v>
       </c>
       <c r="B331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C331" t="n">
         <v>0.4140625</v>
@@ -5075,7 +5075,7 @@
         <v>354</v>
       </c>
       <c r="B332" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C332" t="n">
         <v>0.3427734375</v>
@@ -5089,7 +5089,7 @@
         <v>355</v>
       </c>
       <c r="B333" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C333" t="n">
         <v>0.341796875</v>
@@ -5103,7 +5103,7 @@
         <v>356</v>
       </c>
       <c r="B334" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C334" t="n">
         <v>0.337890625</v>
@@ -5117,7 +5117,7 @@
         <v>357</v>
       </c>
       <c r="B335" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C335" t="n">
         <v>0.3525390625</v>
@@ -5131,7 +5131,7 @@
         <v>358</v>
       </c>
       <c r="B336" t="n">
-        <v>0</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="C336" t="n">
         <v>0.31201171875</v>
@@ -5145,7 +5145,7 @@
         <v>359</v>
       </c>
       <c r="B337" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C337" t="n">
         <v>0.390625</v>
@@ -5159,7 +5159,7 @@
         <v>360</v>
       </c>
       <c r="B338" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C338" t="n">
         <v>0.3330078125</v>
@@ -5173,7 +5173,7 @@
         <v>361</v>
       </c>
       <c r="B339" t="n">
-        <v>0</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C339" t="n">
         <v>0.3092447916666667</v>
@@ -5187,7 +5187,7 @@
         <v>362</v>
       </c>
       <c r="B340" t="n">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C340" t="n">
         <v>0.3365885416666667</v>
@@ -5201,7 +5201,7 @@
         <v>363</v>
       </c>
       <c r="B341" t="n">
-        <v>0</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C341" t="n">
         <v>0.2926432291666667</v>
@@ -5215,7 +5215,7 @@
         <v>364</v>
       </c>
       <c r="B342" t="n">
-        <v>0</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C342" t="n">
         <v>0.2958984375</v>
@@ -5229,7 +5229,7 @@
         <v>365</v>
       </c>
       <c r="B343" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C343" t="n">
         <v>0.2923177083333333</v>
@@ -5243,7 +5243,7 @@
         <v>366</v>
       </c>
       <c r="B344" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C344" t="n">
         <v>0.283203125</v>
@@ -5257,7 +5257,7 @@
         <v>367</v>
       </c>
       <c r="B345" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C345" t="n">
         <v>0.2600911458333333</v>
@@ -5271,7 +5271,7 @@
         <v>368</v>
       </c>
       <c r="B346" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C346" t="n">
         <v>0.21875</v>

--- a/GOLDEN_DATASET/data/cached_scores/sample_dataset_cached_scores.xlsx
+++ b/GOLDEN_DATASET/data/cached_scores/sample_dataset_cached_scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5555555555555555</v>
+        <v>0.7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5625</v>
+        <v>0.556640625</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.52</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5234375</v>
+        <v>0.513671875</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4555555555555555</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5126953125</v>
+        <v>0.508984375</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C14" t="n">
-        <v>0.56982421875</v>
+        <v>0.5826822916666666</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -679,13 +679,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="C18" t="n">
-        <v>0.52587890625</v>
+        <v>0.5305989583333334</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -721,13 +721,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="C21" t="n">
-        <v>0.505859375</v>
+        <v>0.5078125</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -746,41 +746,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6888888888888888</v>
       </c>
       <c r="C23" t="n">
-        <v>0.498046875</v>
+        <v>0.5423177083333334</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n">
-        <v>0.6888888888888888</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5423177083333334</v>
+        <v>0.4833984375</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n">
-        <v>0.6</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4869791666666667</v>
+        <v>0.5345052083333334</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
@@ -788,13 +788,13 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5345052083333334</v>
+        <v>0.53515625</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
@@ -802,153 +802,153 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5234375</v>
+        <v>0.5517578125</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5266927083333334</v>
+        <v>0.4736328125</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.3466666666666667</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.491796875</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n">
-        <v>0.3444444444444445</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4869791666666667</v>
+        <v>0.5169270833333334</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5009765625</v>
+        <v>0.5279947916666666</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C32" t="n">
-        <v>0.50830078125</v>
+        <v>0.5247395833333334</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n">
-        <v>0.5</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="C33" t="n">
-        <v>0.50244140625</v>
+        <v>0.5221354166666666</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="C34" t="n">
-        <v>0.50048828125</v>
+        <v>0.4541015625</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="C35" t="n">
-        <v>0.447265625</v>
+        <v>0.5009765625</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>0.4</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4875</v>
+        <v>0.4443359375</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.5111111111111112</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4401041666666667</v>
+        <v>0.5</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
@@ -956,27 +956,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4794921875</v>
+        <v>0.4404296875</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4309895833333333</v>
+        <v>0.439453125</v>
       </c>
       <c r="D39" t="n">
         <v>3</v>
@@ -984,13 +984,13 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="C40" t="n">
-        <v>0.439453125</v>
+        <v>0.435546875</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
@@ -998,13 +998,13 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C41" t="n">
-        <v>0.435546875</v>
+        <v>0.431640625</v>
       </c>
       <c r="D41" t="n">
         <v>3</v>
@@ -1012,13 +1012,13 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B42" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C42" t="n">
-        <v>0.431640625</v>
+        <v>0.4296875</v>
       </c>
       <c r="D42" t="n">
         <v>3</v>
@@ -1026,27 +1026,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43" t="n">
-        <v>0.55</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="C43" t="n">
-        <v>0.42138671875</v>
+        <v>0.54296875</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="C44" t="n">
-        <v>0.54296875</v>
+        <v>0.5</v>
       </c>
       <c r="D44" t="n">
         <v>3</v>
@@ -1054,251 +1054,251 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B45" t="n">
-        <v>0.4</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C45" t="n">
-        <v>0.47265625</v>
+        <v>0.4228515625</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46" t="n">
-        <v>0.5555555555555555</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C46" t="n">
-        <v>0.41015625</v>
+        <v>0.421875</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B47" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4029947916666667</v>
+        <v>0.41796875</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B48" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="C48" t="n">
-        <v>0.41796875</v>
+        <v>0.4778645833333333</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B49" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4778645833333333</v>
+        <v>0.419921875</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B50" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4533333333333333</v>
       </c>
       <c r="C50" t="n">
-        <v>0.419921875</v>
+        <v>0.4640625</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B51" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4640625</v>
+        <v>0.5810546875</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B52" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4133333333333333</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5810546875</v>
+        <v>0.46171875</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B53" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C53" t="n">
-        <v>0.46171875</v>
+        <v>0.416015625</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B54" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C54" t="n">
-        <v>0.416015625</v>
+        <v>0.4189453125</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B55" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="C55" t="n">
-        <v>0.4189453125</v>
+        <v>0.4147135416666667</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B56" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C56" t="n">
-        <v>0.40185546875</v>
+        <v>0.4095052083333333</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B57" t="n">
-        <v>0.4833333333333334</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3974609375</v>
+        <v>0.404296875</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B58" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.55</v>
       </c>
       <c r="C58" t="n">
-        <v>0.380859375</v>
+        <v>0.5263671875</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B59" t="n">
-        <v>0.55</v>
+        <v>0.3904761904761904</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5263671875</v>
+        <v>0.4347098214285715</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B60" t="n">
-        <v>0.3904761904761904</v>
+        <v>0.6</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4347098214285715</v>
+        <v>0.4033203125</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B61" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3854166666666667</v>
+        <v>0.4013671875</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B62" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4013671875</v>
+        <v>0.4345703125</v>
       </c>
       <c r="D62" t="n">
         <v>2</v>
@@ -1306,27 +1306,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B63" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4345703125</v>
+        <v>0.423828125</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B64" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C64" t="n">
-        <v>0.423828125</v>
+        <v>0.4231770833333333</v>
       </c>
       <c r="D64" t="n">
         <v>3</v>
@@ -1334,111 +1334,111 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B65" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4231770833333333</v>
+        <v>0.4654947916666667</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B66" t="n">
-        <v>0.4777777777777778</v>
+        <v>0.9</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4654947916666667</v>
+        <v>0.5166015625</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B67" t="n">
-        <v>0.9</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5166015625</v>
+        <v>0.46484375</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B68" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C68" t="n">
-        <v>0.46484375</v>
+        <v>0.47265625</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>0.55</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C69" t="n">
-        <v>0.44140625</v>
+        <v>0.3938802083333333</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B70" t="n">
-        <v>0.5555555555555555</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3938802083333333</v>
+        <v>0.3896484375</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B71" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3896484375</v>
+        <v>0.41015625</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B72" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C72" t="n">
-        <v>0.41015625</v>
+        <v>0.46484375</v>
       </c>
       <c r="D72" t="n">
         <v>3</v>
@@ -1446,27 +1446,27 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B73" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6</v>
       </c>
       <c r="C73" t="n">
-        <v>0.46484375</v>
+        <v>0.4677734375</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B74" t="n">
-        <v>0.6</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4677734375</v>
+        <v>0.50390625</v>
       </c>
       <c r="D74" t="n">
         <v>2</v>
@@ -1474,13 +1474,13 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B75" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C75" t="n">
-        <v>0.50390625</v>
+        <v>0.4990234375</v>
       </c>
       <c r="D75" t="n">
         <v>2</v>
@@ -1488,13 +1488,13 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B76" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4990234375</v>
+        <v>0.46484375</v>
       </c>
       <c r="D76" t="n">
         <v>2</v>
@@ -1502,55 +1502,55 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B77" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.46484375</v>
+        <v>0.4036458333333333</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B78" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4036458333333333</v>
+        <v>0.36328125</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="C79" t="n">
-        <v>0.36328125</v>
+        <v>0.5690104166666666</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B80" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="C80" t="n">
-        <v>0.5690104166666666</v>
+        <v>0.3704427083333333</v>
       </c>
       <c r="D80" t="n">
         <v>3</v>
@@ -1558,41 +1558,41 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B81" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.7</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3704427083333333</v>
+        <v>0.453125</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B82" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="C82" t="n">
-        <v>0.34375</v>
+        <v>0.4521484375</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B83" t="n">
-        <v>0.7</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C83" t="n">
-        <v>0.453125</v>
+        <v>0.490234375</v>
       </c>
       <c r="D83" t="n">
         <v>2</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B84" t="n">
-        <v>0.7</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4521484375</v>
+        <v>0.4501953125</v>
       </c>
       <c r="D84" t="n">
         <v>2</v>
@@ -1614,83 +1614,83 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B85" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="C85" t="n">
-        <v>0.490234375</v>
+        <v>0.48671875</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B86" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C86" t="n">
-        <v>0.4501953125</v>
+        <v>0.55078125</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B87" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="C87" t="n">
-        <v>0.48671875</v>
+        <v>0.443359375</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B88" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.4</v>
       </c>
       <c r="C88" t="n">
-        <v>0.55078125</v>
+        <v>0.4384765625</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B89" t="n">
-        <v>0.4</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C89" t="n">
-        <v>0.443359375</v>
+        <v>0.4892578125</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B90" t="n">
-        <v>0.4</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4384765625</v>
+        <v>0.4765625</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
@@ -1698,13 +1698,13 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B91" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4892578125</v>
+        <v>0.56689453125</v>
       </c>
       <c r="D91" t="n">
         <v>4</v>
@@ -1712,69 +1712,69 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B92" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C92" t="n">
-        <v>0.4765625</v>
+        <v>0.4856770833333333</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B93" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="C93" t="n">
-        <v>0.56689453125</v>
+        <v>0.5361328125</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B94" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C94" t="n">
-        <v>0.4856770833333333</v>
+        <v>0.341796875</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B95" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C95" t="n">
-        <v>0.5361328125</v>
+        <v>0.455078125</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B96" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="C96" t="n">
-        <v>0.341796875</v>
+        <v>0.3623046875</v>
       </c>
       <c r="D96" t="n">
         <v>2</v>
@@ -1782,27 +1782,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B97" t="n">
-        <v>0.3</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C97" t="n">
-        <v>0.455078125</v>
+        <v>0.3623046875</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B98" t="n">
-        <v>0.5</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3623046875</v>
+        <v>0.427734375</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
@@ -1810,55 +1810,55 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B99" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="C99" t="n">
-        <v>0.3623046875</v>
+        <v>0.4996744791666667</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B100" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="C100" t="n">
-        <v>0.427734375</v>
+        <v>0.55908203125</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B101" t="n">
-        <v>0.4190476190476191</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C101" t="n">
-        <v>0.5159040178571429</v>
+        <v>0.4680989583333333</v>
       </c>
       <c r="D101" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B102" t="n">
-        <v>0.5166666666666666</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="C102" t="n">
-        <v>0.55908203125</v>
+        <v>0.43115234375</v>
       </c>
       <c r="D102" t="n">
         <v>4</v>
@@ -1866,13 +1866,13 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B103" t="n">
-        <v>0.5555555555555555</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="C103" t="n">
-        <v>0.4680989583333333</v>
+        <v>0.4615885416666667</v>
       </c>
       <c r="D103" t="n">
         <v>3</v>
@@ -1880,69 +1880,69 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B104" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C104" t="n">
-        <v>0.43115234375</v>
+        <v>0.4713541666666667</v>
       </c>
       <c r="D104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B105" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C105" t="n">
-        <v>0.4615885416666667</v>
+        <v>0.44970703125</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B106" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C106" t="n">
-        <v>0.43505859375</v>
+        <v>0.484375</v>
       </c>
       <c r="D106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B107" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="C107" t="n">
-        <v>0.44970703125</v>
+        <v>0.4837239583333333</v>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B108" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="C108" t="n">
-        <v>0.484375</v>
+        <v>0.3603515625</v>
       </c>
       <c r="D108" t="n">
         <v>2</v>
@@ -1950,13 +1950,13 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B109" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4837239583333333</v>
+        <v>0.44921875</v>
       </c>
       <c r="D109" t="n">
         <v>3</v>
@@ -1964,41 +1964,41 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B110" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3603515625</v>
+        <v>0.4446614583333333</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B111" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333334</v>
       </c>
       <c r="C111" t="n">
-        <v>0.44921875</v>
+        <v>0.4833984375</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B112" t="n">
-        <v>0.6</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="C112" t="n">
-        <v>0.4446614583333333</v>
+        <v>0.3600260416666667</v>
       </c>
       <c r="D112" t="n">
         <v>3</v>
@@ -2006,27 +2006,27 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B113" t="n">
-        <v>0.5333333333333334</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="C113" t="n">
-        <v>0.4833984375</v>
+        <v>0.4671875</v>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B114" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3600260416666667</v>
+        <v>0.4466145833333333</v>
       </c>
       <c r="D114" t="n">
         <v>3</v>
@@ -2034,41 +2034,41 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B115" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C115" t="n">
-        <v>0.4671875</v>
+        <v>0.4329427083333333</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B116" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="C116" t="n">
-        <v>0.4466145833333333</v>
+        <v>0.40966796875</v>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B117" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C117" t="n">
-        <v>0.4329427083333333</v>
+        <v>0.4173177083333333</v>
       </c>
       <c r="D117" t="n">
         <v>3</v>
@@ -2076,41 +2076,41 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B118" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C118" t="n">
-        <v>0.40966796875</v>
+        <v>0.412109375</v>
       </c>
       <c r="D118" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B119" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C119" t="n">
-        <v>0.4173177083333333</v>
+        <v>0.462890625</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B120" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="C120" t="n">
-        <v>0.412109375</v>
+        <v>0.404296875</v>
       </c>
       <c r="D120" t="n">
         <v>3</v>
@@ -2118,27 +2118,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B121" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="C121" t="n">
-        <v>0.462890625</v>
+        <v>0.3984375</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B122" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C122" t="n">
-        <v>0.404296875</v>
+        <v>0.396484375</v>
       </c>
       <c r="D122" t="n">
         <v>3</v>
@@ -2146,13 +2146,13 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B123" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3984375</v>
+        <v>0.3938802083333333</v>
       </c>
       <c r="D123" t="n">
         <v>3</v>
@@ -2160,13 +2160,13 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B124" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C124" t="n">
-        <v>0.396484375</v>
+        <v>0.392578125</v>
       </c>
       <c r="D124" t="n">
         <v>3</v>
@@ -2174,13 +2174,13 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B125" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C125" t="n">
-        <v>0.3938802083333333</v>
+        <v>0.3873697916666667</v>
       </c>
       <c r="D125" t="n">
         <v>3</v>
@@ -2188,13 +2188,13 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B126" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="C126" t="n">
-        <v>0.392578125</v>
+        <v>0.3828125</v>
       </c>
       <c r="D126" t="n">
         <v>3</v>
@@ -2202,13 +2202,13 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B127" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="C127" t="n">
-        <v>0.3873697916666667</v>
+        <v>0.375</v>
       </c>
       <c r="D127" t="n">
         <v>3</v>
@@ -2216,13 +2216,13 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B128" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C128" t="n">
-        <v>0.3828125</v>
+        <v>0.3684895833333333</v>
       </c>
       <c r="D128" t="n">
         <v>3</v>
@@ -2230,13 +2230,13 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B129" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="C129" t="n">
-        <v>0.375</v>
+        <v>0.3365885416666667</v>
       </c>
       <c r="D129" t="n">
         <v>3</v>
@@ -2244,69 +2244,69 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B130" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.48</v>
       </c>
       <c r="C130" t="n">
-        <v>0.3684895833333333</v>
+        <v>0.407421875</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B131" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.4095238095238096</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3365885416666667</v>
+        <v>0.423828125</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B132" t="n">
-        <v>0.48</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C132" t="n">
-        <v>0.407421875</v>
+        <v>0.3857421875</v>
       </c>
       <c r="D132" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B133" t="n">
-        <v>0.4095238095238096</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C133" t="n">
-        <v>0.423828125</v>
+        <v>0.494140625</v>
       </c>
       <c r="D133" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B134" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C134" t="n">
-        <v>0.3857421875</v>
+        <v>0.3818359375</v>
       </c>
       <c r="D134" t="n">
         <v>2</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B135" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="C135" t="n">
-        <v>0.494140625</v>
+        <v>0.48828125</v>
       </c>
       <c r="D135" t="n">
         <v>1</v>
@@ -2328,83 +2328,83 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B136" t="n">
         <v>0.6333333333333333</v>
       </c>
       <c r="C136" t="n">
-        <v>0.3818359375</v>
+        <v>0.4638671875</v>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B137" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="C137" t="n">
-        <v>0.48828125</v>
+        <v>0.3916015625</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B138" t="n">
-        <v>0.5333333333333334</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4828125</v>
+        <v>0.4291294642857143</v>
       </c>
       <c r="D138" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B139" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="C139" t="n">
-        <v>0.3916015625</v>
+        <v>0.416015625</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B140" t="n">
-        <v>0.4416666666666667</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C140" t="n">
-        <v>0.44140625</v>
+        <v>0.4524739583333333</v>
       </c>
       <c r="D140" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B141" t="n">
-        <v>0.3185185185185185</v>
+        <v>0.4962962962962963</v>
       </c>
       <c r="C141" t="n">
-        <v>0.4136284722222222</v>
+        <v>0.4227430555555556</v>
       </c>
       <c r="D141" t="n">
         <v>9</v>
@@ -2412,13 +2412,13 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B142" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.6</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4524739583333333</v>
+        <v>0.3697916666666667</v>
       </c>
       <c r="D142" t="n">
         <v>3</v>
@@ -2426,83 +2426,83 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B143" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C143" t="n">
-        <v>0.426171875</v>
+        <v>0.4134114583333333</v>
       </c>
       <c r="D143" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B144" t="n">
-        <v>0.6</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="C144" t="n">
-        <v>0.3697916666666667</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B145" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C145" t="n">
-        <v>0.4150390625</v>
+        <v>0.3681640625</v>
       </c>
       <c r="D145" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B146" t="n">
-        <v>0.3</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C146" t="n">
-        <v>0.411376953125</v>
+        <v>0.359375</v>
       </c>
       <c r="D146" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B147" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="C147" t="n">
-        <v>0.3681640625</v>
+        <v>0.3118489583333333</v>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B148" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C148" t="n">
-        <v>0.359375</v>
+        <v>0.36328125</v>
       </c>
       <c r="D148" t="n">
         <v>3</v>
@@ -2510,97 +2510,97 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B149" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C149" t="n">
-        <v>0.3118489583333333</v>
+        <v>0.408203125</v>
       </c>
       <c r="D149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B150" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="C150" t="n">
-        <v>0.36328125</v>
+        <v>0.375390625</v>
       </c>
       <c r="D150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B151" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4095238095238095</v>
       </c>
       <c r="C151" t="n">
-        <v>0.408203125</v>
+        <v>0.4012276785714285</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B152" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.4190476190476191</v>
       </c>
       <c r="C152" t="n">
-        <v>0.3798828125</v>
+        <v>0.4095982142857143</v>
       </c>
       <c r="D152" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B153" t="n">
-        <v>0.3833333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="C153" t="n">
-        <v>0.39990234375</v>
+        <v>0.365234375</v>
       </c>
       <c r="D153" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B154" t="n">
-        <v>0.375</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="C154" t="n">
-        <v>0.39599609375</v>
+        <v>0.3623046875</v>
       </c>
       <c r="D154" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B155" t="n">
-        <v>0.9</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="C155" t="n">
-        <v>0.365234375</v>
+        <v>0.4384765625</v>
       </c>
       <c r="D155" t="n">
         <v>2</v>
@@ -2608,27 +2608,27 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B156" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C156" t="n">
-        <v>0.3623046875</v>
+        <v>0.3528645833333333</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B157" t="n">
-        <v>0.4444444444444445</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C157" t="n">
-        <v>0.4173177083333333</v>
+        <v>0.3411458333333333</v>
       </c>
       <c r="D157" t="n">
         <v>3</v>
@@ -2636,27 +2636,27 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B158" t="n">
-        <v>0.5555555555555555</v>
+        <v>0.3238095238095238</v>
       </c>
       <c r="C158" t="n">
-        <v>0.3528645833333333</v>
+        <v>0.3959263392857143</v>
       </c>
       <c r="D158" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B159" t="n">
         <v>0.6222222222222222</v>
       </c>
       <c r="C159" t="n">
-        <v>0.3411458333333333</v>
+        <v>0.3938802083333333</v>
       </c>
       <c r="D159" t="n">
         <v>3</v>
@@ -2664,41 +2664,41 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B160" t="n">
-        <v>0.2916666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C160" t="n">
-        <v>0.38916015625</v>
+        <v>0.345703125</v>
       </c>
       <c r="D160" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B161" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C161" t="n">
-        <v>0.3938802083333333</v>
+        <v>0.3828125</v>
       </c>
       <c r="D161" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B162" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C162" t="n">
-        <v>0.345703125</v>
+        <v>0.3525390625</v>
       </c>
       <c r="D162" t="n">
         <v>2</v>
@@ -2706,97 +2706,97 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B163" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="C163" t="n">
-        <v>0.3828125</v>
+        <v>0.3740234375</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B164" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C164" t="n">
-        <v>0.3525390625</v>
+        <v>0.3404947916666667</v>
       </c>
       <c r="D164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B165" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C165" t="n">
-        <v>0.3740234375</v>
+        <v>0.3821614583333333</v>
       </c>
       <c r="D165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B166" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C166" t="n">
-        <v>0.3404947916666667</v>
+        <v>0.330078125</v>
       </c>
       <c r="D166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B167" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C167" t="n">
-        <v>0.3821614583333333</v>
+        <v>0.38525390625</v>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B168" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C168" t="n">
-        <v>0.330078125</v>
+        <v>0.4368489583333333</v>
       </c>
       <c r="D168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B169" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5166666666666667</v>
       </c>
       <c r="C169" t="n">
-        <v>0.38525390625</v>
+        <v>0.353515625</v>
       </c>
       <c r="D169" t="n">
         <v>4</v>
@@ -2804,13 +2804,13 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B170" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C170" t="n">
-        <v>0.4368489583333333</v>
+        <v>0.359375</v>
       </c>
       <c r="D170" t="n">
         <v>3</v>
@@ -2818,97 +2818,97 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B171" t="n">
-        <v>0.5166666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C171" t="n">
-        <v>0.353515625</v>
+        <v>0.3782552083333333</v>
       </c>
       <c r="D171" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B172" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C172" t="n">
-        <v>0.359375</v>
+        <v>0.3837890625</v>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B173" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C173" t="n">
-        <v>0.3782552083333333</v>
+        <v>0.37841796875</v>
       </c>
       <c r="D173" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B174" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C174" t="n">
-        <v>0.3837890625</v>
+        <v>0.3776041666666667</v>
       </c>
       <c r="D174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B175" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C175" t="n">
-        <v>0.37841796875</v>
+        <v>0.3987630208333333</v>
       </c>
       <c r="D175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B176" t="n">
-        <v>0.688888888888889</v>
+        <v>1</v>
       </c>
       <c r="C176" t="n">
-        <v>0.3776041666666667</v>
+        <v>0.23828125</v>
       </c>
       <c r="D176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B177" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="C177" t="n">
-        <v>0.3987630208333333</v>
+        <v>0.4147135416666667</v>
       </c>
       <c r="D177" t="n">
         <v>3</v>
@@ -2916,27 +2916,27 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C178" t="n">
-        <v>0.23828125</v>
+        <v>0.431640625</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B179" t="n">
-        <v>0.6444444444444444</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4147135416666667</v>
+        <v>0.3912760416666667</v>
       </c>
       <c r="D179" t="n">
         <v>3</v>
@@ -2944,139 +2944,139 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B180" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C180" t="n">
-        <v>0.431640625</v>
+        <v>0.4622395833333333</v>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B181" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C181" t="n">
-        <v>0.3912760416666667</v>
+        <v>0.4111328125</v>
       </c>
       <c r="D181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B182" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.9</v>
       </c>
       <c r="C182" t="n">
-        <v>0.4622395833333333</v>
+        <v>0.4091796875</v>
       </c>
       <c r="D182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B183" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="C183" t="n">
-        <v>0.4111328125</v>
+        <v>0.3890625</v>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B184" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C184" t="n">
-        <v>0.4091796875</v>
+        <v>0.2578125</v>
       </c>
       <c r="D184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B185" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C185" t="n">
-        <v>0.3890625</v>
+        <v>0.3828125</v>
       </c>
       <c r="D185" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B186" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C186" t="n">
-        <v>0.2578125</v>
+        <v>0.3759765625</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B187" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C187" t="n">
-        <v>0.3828125</v>
+        <v>0.431640625</v>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B188" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3759765625</v>
+        <v>0.548828125</v>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B189" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C189" t="n">
-        <v>0.431640625</v>
+        <v>0.544921875</v>
       </c>
       <c r="D189" t="n">
         <v>2</v>
@@ -3084,13 +3084,13 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B190" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C190" t="n">
-        <v>0.548828125</v>
+        <v>0.4697265625</v>
       </c>
       <c r="D190" t="n">
         <v>2</v>
@@ -3098,55 +3098,55 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B191" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="C191" t="n">
-        <v>0.544921875</v>
+        <v>0.501953125</v>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B192" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C192" t="n">
-        <v>0.4697265625</v>
+        <v>0.4889322916666667</v>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B193" t="n">
-        <v>0.6444444444444445</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C193" t="n">
-        <v>0.501953125</v>
+        <v>0.53125</v>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B194" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8222222222222223</v>
       </c>
       <c r="C194" t="n">
-        <v>0.4889322916666667</v>
+        <v>0.4830729166666667</v>
       </c>
       <c r="D194" t="n">
         <v>3</v>
@@ -3154,41 +3154,41 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B195" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C195" t="n">
-        <v>0.53125</v>
+        <v>0.4609375</v>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B196" t="n">
-        <v>0.8222222222222223</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C196" t="n">
-        <v>0.4830729166666667</v>
+        <v>0.4736328125</v>
       </c>
       <c r="D196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B197" t="n">
-        <v>0.9</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C197" t="n">
-        <v>0.4609375</v>
+        <v>0.458984375</v>
       </c>
       <c r="D197" t="n">
         <v>2</v>
@@ -3196,41 +3196,41 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B198" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="C198" t="n">
-        <v>0.4736328125</v>
+        <v>0.3912760416666667</v>
       </c>
       <c r="D198" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B199" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C199" t="n">
-        <v>0.458984375</v>
+        <v>0.4654947916666667</v>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B200" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C200" t="n">
-        <v>0.3912760416666667</v>
+        <v>0.4622395833333333</v>
       </c>
       <c r="D200" t="n">
         <v>3</v>
@@ -3238,27 +3238,27 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B201" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C201" t="n">
-        <v>0.4654947916666667</v>
+        <v>0.4453125</v>
       </c>
       <c r="D201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B202" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C202" t="n">
-        <v>0.4622395833333333</v>
+        <v>0.462890625</v>
       </c>
       <c r="D202" t="n">
         <v>3</v>
@@ -3266,41 +3266,41 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B203" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C203" t="n">
-        <v>0.4453125</v>
+        <v>0.4576822916666667</v>
       </c>
       <c r="D203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B204" t="n">
-        <v>0.688888888888889</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="C204" t="n">
-        <v>0.462890625</v>
+        <v>0.3987630208333333</v>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B205" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="C205" t="n">
-        <v>0.4576822916666667</v>
+        <v>0.4505208333333333</v>
       </c>
       <c r="D205" t="n">
         <v>3</v>
@@ -3308,69 +3308,69 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B206" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C206" t="n">
-        <v>0.3897879464285715</v>
+        <v>0.4306640625</v>
       </c>
       <c r="D206" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B207" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C207" t="n">
-        <v>0.4505208333333333</v>
+        <v>0.4296875</v>
       </c>
       <c r="D207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B208" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C208" t="n">
-        <v>0.4306640625</v>
+        <v>0.4010416666666667</v>
       </c>
       <c r="D208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B209" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C209" t="n">
-        <v>0.4296875</v>
+        <v>0.443359375</v>
       </c>
       <c r="D209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B210" t="n">
-        <v>0.688888888888889</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C210" t="n">
-        <v>0.4010416666666667</v>
+        <v>0.4251302083333333</v>
       </c>
       <c r="D210" t="n">
         <v>3</v>
@@ -3378,83 +3378,83 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B211" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C211" t="n">
-        <v>0.443359375</v>
+        <v>0.470703125</v>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B212" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.8</v>
       </c>
       <c r="C212" t="n">
-        <v>0.4251302083333333</v>
+        <v>0.46875</v>
       </c>
       <c r="D212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B213" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="C213" t="n">
-        <v>0.470703125</v>
+        <v>0.439453125</v>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B214" t="n">
-        <v>0.8</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C214" t="n">
-        <v>0.46875</v>
+        <v>0.4912109375</v>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B215" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C215" t="n">
-        <v>0.439453125</v>
+        <v>0.48046875</v>
       </c>
       <c r="D215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B216" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C216" t="n">
-        <v>0.4912109375</v>
+        <v>0.4794921875</v>
       </c>
       <c r="D216" t="n">
         <v>2</v>
@@ -3462,13 +3462,13 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B217" t="n">
-        <v>0.5333333333333333</v>
+        <v>1</v>
       </c>
       <c r="C217" t="n">
-        <v>0.48046875</v>
+        <v>0.412109375</v>
       </c>
       <c r="D217" t="n">
         <v>2</v>
@@ -3476,27 +3476,27 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B218" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C218" t="n">
-        <v>0.4794921875</v>
+        <v>0.462890625</v>
       </c>
       <c r="D218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B219" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C219" t="n">
-        <v>0.412109375</v>
+        <v>0.41015625</v>
       </c>
       <c r="D219" t="n">
         <v>2</v>
@@ -3504,181 +3504,181 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B220" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C220" t="n">
-        <v>0.462890625</v>
+        <v>0.3854166666666667</v>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B221" t="n">
-        <v>0.8</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="C221" t="n">
-        <v>0.41015625</v>
+        <v>0.395703125</v>
       </c>
       <c r="D221" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B222" t="n">
-        <v>0.7111111111111111</v>
+        <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>0.3854166666666667</v>
+        <v>0.3935546875</v>
       </c>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B223" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="C223" t="n">
-        <v>0.395703125</v>
+        <v>0.4153645833333333</v>
       </c>
       <c r="D223" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B224" t="n">
-        <v>1</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="C224" t="n">
-        <v>0.3935546875</v>
+        <v>0.3736979166666667</v>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B225" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.4</v>
       </c>
       <c r="C225" t="n">
-        <v>0.4153645833333333</v>
+        <v>0.2578125</v>
       </c>
       <c r="D225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B226" t="n">
-        <v>0.3523809523809524</v>
+        <v>0.3818181818181818</v>
       </c>
       <c r="C226" t="n">
-        <v>0.3624441964285715</v>
+        <v>0.3606178977272727</v>
       </c>
       <c r="D226" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B227" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="C227" t="n">
-        <v>0.2578125</v>
+        <v>0.451171875</v>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B228" t="n">
-        <v>0.3538461538461539</v>
+        <v>0.4266666666666666</v>
       </c>
       <c r="C228" t="n">
-        <v>0.3533653846153846</v>
+        <v>0.37578125</v>
       </c>
       <c r="D228" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B229" t="n">
-        <v>0.7</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="C229" t="n">
-        <v>0.451171875</v>
+        <v>0.3802083333333333</v>
       </c>
       <c r="D229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B230" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C230" t="n">
-        <v>0.3665364583333333</v>
+        <v>0.3701171875</v>
       </c>
       <c r="D230" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B231" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="C231" t="n">
-        <v>0.348046875</v>
+        <v>0.35107421875</v>
       </c>
       <c r="D231" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B232" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C232" t="n">
-        <v>0.3701171875</v>
+        <v>0.3935546875</v>
       </c>
       <c r="D232" t="n">
         <v>2</v>
@@ -3686,69 +3686,69 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B233" t="n">
-        <v>0.4</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="C233" t="n">
-        <v>0.35107421875</v>
+        <v>0.4108072916666667</v>
       </c>
       <c r="D233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B234" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="C234" t="n">
-        <v>0.3935546875</v>
+        <v>0.363525390625</v>
       </c>
       <c r="D234" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B235" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C235" t="n">
-        <v>0.4108072916666667</v>
+        <v>0.34619140625</v>
       </c>
       <c r="D235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B236" t="n">
-        <v>0.5166666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="C236" t="n">
-        <v>0.363525390625</v>
+        <v>0.357421875</v>
       </c>
       <c r="D236" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B237" t="n">
         <v>0.6333333333333333</v>
       </c>
       <c r="C237" t="n">
-        <v>0.34619140625</v>
+        <v>0.375</v>
       </c>
       <c r="D237" t="n">
         <v>2</v>
@@ -3756,13 +3756,13 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B238" t="n">
-        <v>0.5</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C238" t="n">
-        <v>0.357421875</v>
+        <v>0.435546875</v>
       </c>
       <c r="D238" t="n">
         <v>2</v>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B239" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C239" t="n">
-        <v>0.375</v>
+        <v>0.43359375</v>
       </c>
       <c r="D239" t="n">
         <v>2</v>
@@ -3784,41 +3784,41 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B240" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="C240" t="n">
-        <v>0.435546875</v>
+        <v>0.3474609375</v>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B241" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="C241" t="n">
-        <v>0.43359375</v>
+        <v>0.427734375</v>
       </c>
       <c r="D241" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B242" t="n">
-        <v>0.3866666666666667</v>
+        <v>0.4133333333333334</v>
       </c>
       <c r="C242" t="n">
-        <v>0.3474609375</v>
+        <v>0.454296875</v>
       </c>
       <c r="D242" t="n">
         <v>5</v>
@@ -3826,139 +3826,139 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B243" t="n">
-        <v>0.5066666666666666</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C243" t="n">
-        <v>0.427734375</v>
+        <v>0.40625</v>
       </c>
       <c r="D243" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B244" t="n">
-        <v>0.4133333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="C244" t="n">
-        <v>0.454296875</v>
+        <v>0.42138671875</v>
       </c>
       <c r="D244" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B245" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="C245" t="n">
-        <v>0.40625</v>
+        <v>0.419921875</v>
       </c>
       <c r="D245" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B246" t="n">
-        <v>0.5</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C246" t="n">
-        <v>0.42138671875</v>
+        <v>0.4169921875</v>
       </c>
       <c r="D246" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B247" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C247" t="n">
-        <v>0.419921875</v>
+        <v>0.447265625</v>
       </c>
       <c r="D247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B248" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.5066666666666667</v>
       </c>
       <c r="C248" t="n">
-        <v>0.4169921875</v>
+        <v>0.429296875</v>
       </c>
       <c r="D248" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B249" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.9</v>
       </c>
       <c r="C249" t="n">
-        <v>0.447265625</v>
+        <v>0.41015625</v>
       </c>
       <c r="D249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B250" t="n">
-        <v>0.5066666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C250" t="n">
-        <v>0.429296875</v>
+        <v>0.4072265625</v>
       </c>
       <c r="D250" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B251" t="n">
-        <v>0.9</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="C251" t="n">
-        <v>0.41015625</v>
+        <v>0.39306640625</v>
       </c>
       <c r="D251" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B252" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C252" t="n">
-        <v>0.4072265625</v>
+        <v>0.40625</v>
       </c>
       <c r="D252" t="n">
         <v>2</v>
@@ -3966,27 +3966,27 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B253" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="C253" t="n">
-        <v>0.39306640625</v>
+        <v>0.41796875</v>
       </c>
       <c r="D253" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B254" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C254" t="n">
-        <v>0.40625</v>
+        <v>0.359375</v>
       </c>
       <c r="D254" t="n">
         <v>2</v>
@@ -3994,27 +3994,27 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B255" t="n">
         <v>0.6</v>
       </c>
       <c r="C255" t="n">
-        <v>0.41796875</v>
+        <v>0.3815104166666667</v>
       </c>
       <c r="D255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B256" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C256" t="n">
-        <v>0.359375</v>
+        <v>0.34765625</v>
       </c>
       <c r="D256" t="n">
         <v>2</v>
@@ -4022,27 +4022,27 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B257" t="n">
-        <v>0.6</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="C257" t="n">
-        <v>0.3815104166666667</v>
+        <v>0.3447265625</v>
       </c>
       <c r="D257" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B258" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="C258" t="n">
-        <v>0.34765625</v>
+        <v>0.4013671875</v>
       </c>
       <c r="D258" t="n">
         <v>2</v>
@@ -4050,55 +4050,55 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B259" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="C259" t="n">
-        <v>0.3447265625</v>
+        <v>0.3795572916666667</v>
       </c>
       <c r="D259" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B260" t="n">
-        <v>0.7</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C260" t="n">
-        <v>0.4013671875</v>
+        <v>0.4915364583333333</v>
       </c>
       <c r="D260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B261" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C261" t="n">
-        <v>0.3795572916666667</v>
+        <v>0.3623046875</v>
       </c>
       <c r="D261" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B262" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="C262" t="n">
-        <v>0.4915364583333333</v>
+        <v>0.423828125</v>
       </c>
       <c r="D262" t="n">
         <v>3</v>
@@ -4106,13 +4106,13 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B263" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C263" t="n">
-        <v>0.3623046875</v>
+        <v>0.353515625</v>
       </c>
       <c r="D263" t="n">
         <v>2</v>
@@ -4120,13 +4120,13 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B264" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C264" t="n">
-        <v>0.423828125</v>
+        <v>0.4674479166666667</v>
       </c>
       <c r="D264" t="n">
         <v>3</v>
@@ -4134,13 +4134,13 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B265" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C265" t="n">
-        <v>0.353515625</v>
+        <v>0.4814453125</v>
       </c>
       <c r="D265" t="n">
         <v>2</v>
@@ -4148,125 +4148,125 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B266" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C266" t="n">
-        <v>0.4674479166666667</v>
+        <v>0.392578125</v>
       </c>
       <c r="D266" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B267" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C267" t="n">
-        <v>0.4814453125</v>
+        <v>0.44482421875</v>
       </c>
       <c r="D267" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B268" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="C268" t="n">
-        <v>0.392578125</v>
+        <v>0.3515625</v>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B269" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C269" t="n">
-        <v>0.44482421875</v>
+        <v>0.380859375</v>
       </c>
       <c r="D269" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B270" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3515625</v>
+        <v>0.36328125</v>
       </c>
       <c r="D270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B271" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C271" t="n">
-        <v>0.380859375</v>
+        <v>0.4361979166666667</v>
       </c>
       <c r="D271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B272" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="C272" t="n">
-        <v>0.36328125</v>
+        <v>0.3515625</v>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B273" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C273" t="n">
-        <v>0.4361979166666667</v>
+        <v>0.330078125</v>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B274" t="n">
-        <v>0.6</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C274" t="n">
-        <v>0.3515625</v>
+        <v>0.36328125</v>
       </c>
       <c r="D274" t="n">
         <v>3</v>
@@ -4274,111 +4274,111 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B275" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="C275" t="n">
-        <v>0.330078125</v>
+        <v>0.3463541666666667</v>
       </c>
       <c r="D275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B276" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C276" t="n">
-        <v>0.36328125</v>
+        <v>0.34375</v>
       </c>
       <c r="D276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B277" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C277" t="n">
-        <v>0.3463541666666667</v>
+        <v>0.3203125</v>
       </c>
       <c r="D277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B278" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C278" t="n">
-        <v>0.34375</v>
+        <v>0.3391927083333333</v>
       </c>
       <c r="D278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B279" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C279" t="n">
-        <v>0.3203125</v>
+        <v>0.3326822916666667</v>
       </c>
       <c r="D279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B280" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="C280" t="n">
-        <v>0.3391927083333333</v>
+        <v>0.330078125</v>
       </c>
       <c r="D280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B281" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C281" t="n">
-        <v>0.3326822916666667</v>
+        <v>0.3743489583333333</v>
       </c>
       <c r="D281" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B282" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.2</v>
       </c>
       <c r="C282" t="n">
-        <v>0.330078125</v>
+        <v>0.3115234375</v>
       </c>
       <c r="D282" t="n">
         <v>2</v>
@@ -4386,41 +4386,41 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B283" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="C283" t="n">
-        <v>0.3743489583333333</v>
+        <v>0.3203125</v>
       </c>
       <c r="D283" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B284" t="n">
-        <v>0.2</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="C284" t="n">
-        <v>0.3115234375</v>
+        <v>0.4114583333333333</v>
       </c>
       <c r="D284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B285" t="n">
-        <v>0.5</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="C285" t="n">
-        <v>0.3203125</v>
+        <v>0.310546875</v>
       </c>
       <c r="D285" t="n">
         <v>4</v>
@@ -4428,13 +4428,13 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B286" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="C286" t="n">
-        <v>0.4114583333333333</v>
+        <v>0.3899739583333333</v>
       </c>
       <c r="D286" t="n">
         <v>3</v>
@@ -4442,13 +4442,13 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B287" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C287" t="n">
-        <v>0.310546875</v>
+        <v>0.37158203125</v>
       </c>
       <c r="D287" t="n">
         <v>4</v>
@@ -4456,55 +4456,55 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B288" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C288" t="n">
-        <v>0.3899739583333333</v>
+        <v>0.37109375</v>
       </c>
       <c r="D288" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B289" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C289" t="n">
-        <v>0.37158203125</v>
+        <v>0.3352864583333333</v>
       </c>
       <c r="D289" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C290" t="n">
-        <v>0.37109375</v>
+        <v>0.4127604166666667</v>
       </c>
       <c r="D290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B291" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C291" t="n">
-        <v>0.3352864583333333</v>
+        <v>0.306640625</v>
       </c>
       <c r="D291" t="n">
         <v>3</v>
@@ -4512,13 +4512,13 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B292" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C292" t="n">
-        <v>0.4127604166666667</v>
+        <v>0.2887369791666667</v>
       </c>
       <c r="D292" t="n">
         <v>3</v>
@@ -4526,13 +4526,13 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B293" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C293" t="n">
-        <v>0.306640625</v>
+        <v>0.3893229166666667</v>
       </c>
       <c r="D293" t="n">
         <v>3</v>
@@ -4540,13 +4540,13 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B294" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="C294" t="n">
-        <v>0.2887369791666667</v>
+        <v>0.2545572916666667</v>
       </c>
       <c r="D294" t="n">
         <v>3</v>
@@ -4554,13 +4554,13 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B295" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="C295" t="n">
-        <v>0.3893229166666667</v>
+        <v>0.2434895833333333</v>
       </c>
       <c r="D295" t="n">
         <v>3</v>
@@ -4568,13 +4568,13 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B296" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.6</v>
       </c>
       <c r="C296" t="n">
-        <v>0.2545572916666667</v>
+        <v>0.2825520833333333</v>
       </c>
       <c r="D296" t="n">
         <v>3</v>
@@ -4582,27 +4582,27 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B297" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="C297" t="n">
-        <v>0.2434895833333333</v>
+        <v>0.38671875</v>
       </c>
       <c r="D297" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B298" t="n">
-        <v>0.6</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="C298" t="n">
-        <v>0.2825520833333333</v>
+        <v>0.4205729166666667</v>
       </c>
       <c r="D298" t="n">
         <v>3</v>
@@ -4610,27 +4610,27 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B299" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="C299" t="n">
-        <v>0.38671875</v>
+        <v>0.37890625</v>
       </c>
       <c r="D299" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B300" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C300" t="n">
-        <v>0.4205729166666667</v>
+        <v>0.3782552083333333</v>
       </c>
       <c r="D300" t="n">
         <v>3</v>
@@ -4638,27 +4638,27 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B301" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.65</v>
       </c>
       <c r="C301" t="n">
-        <v>0.37890625</v>
+        <v>0.365234375</v>
       </c>
       <c r="D301" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B302" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C302" t="n">
-        <v>0.3782552083333333</v>
+        <v>0.3411458333333333</v>
       </c>
       <c r="D302" t="n">
         <v>3</v>
@@ -4666,27 +4666,27 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B303" t="n">
-        <v>0.65</v>
+        <v>0.6888888888888888</v>
       </c>
       <c r="C303" t="n">
-        <v>0.365234375</v>
+        <v>0.333984375</v>
       </c>
       <c r="D303" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B304" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6888888888888888</v>
       </c>
       <c r="C304" t="n">
-        <v>0.3411458333333333</v>
+        <v>0.3274739583333333</v>
       </c>
       <c r="D304" t="n">
         <v>3</v>
@@ -4694,13 +4694,13 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B305" t="n">
-        <v>0.6888888888888888</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C305" t="n">
-        <v>0.333984375</v>
+        <v>0.33984375</v>
       </c>
       <c r="D305" t="n">
         <v>3</v>
@@ -4708,13 +4708,13 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B306" t="n">
-        <v>0.6888888888888888</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C306" t="n">
-        <v>0.3274739583333333</v>
+        <v>0.3352864583333333</v>
       </c>
       <c r="D306" t="n">
         <v>3</v>
@@ -4722,13 +4722,13 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B307" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="C307" t="n">
-        <v>0.33984375</v>
+        <v>0.3209635416666667</v>
       </c>
       <c r="D307" t="n">
         <v>3</v>
@@ -4736,27 +4736,27 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B308" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C308" t="n">
-        <v>0.3352864583333333</v>
+        <v>0.4462890625</v>
       </c>
       <c r="D308" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B309" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C309" t="n">
-        <v>0.3209635416666667</v>
+        <v>0.404296875</v>
       </c>
       <c r="D309" t="n">
         <v>3</v>
@@ -4764,27 +4764,27 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B310" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="C310" t="n">
-        <v>0.4462890625</v>
+        <v>0.3899739583333333</v>
       </c>
       <c r="D310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B311" t="n">
-        <v>0.688888888888889</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C311" t="n">
-        <v>0.404296875</v>
+        <v>0.380859375</v>
       </c>
       <c r="D311" t="n">
         <v>3</v>
@@ -4792,13 +4792,13 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B312" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C312" t="n">
-        <v>0.3899739583333333</v>
+        <v>0.373046875</v>
       </c>
       <c r="D312" t="n">
         <v>3</v>
@@ -4806,13 +4806,13 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B313" t="n">
-        <v>0.7111111111111111</v>
+        <v>1</v>
       </c>
       <c r="C313" t="n">
-        <v>0.380859375</v>
+        <v>0.3697916666666667</v>
       </c>
       <c r="D313" t="n">
         <v>3</v>
@@ -4820,13 +4820,13 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B314" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C314" t="n">
-        <v>0.373046875</v>
+        <v>0.3606770833333333</v>
       </c>
       <c r="D314" t="n">
         <v>3</v>
@@ -4834,13 +4834,13 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B315" t="n">
-        <v>1</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C315" t="n">
-        <v>0.3697916666666667</v>
+        <v>0.357421875</v>
       </c>
       <c r="D315" t="n">
         <v>3</v>
@@ -4848,13 +4848,13 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B316" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C316" t="n">
-        <v>0.3606770833333333</v>
+        <v>0.353515625</v>
       </c>
       <c r="D316" t="n">
         <v>3</v>
@@ -4862,13 +4862,13 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B317" t="n">
         <v>0.9777777777777779</v>
       </c>
       <c r="C317" t="n">
-        <v>0.357421875</v>
+        <v>0.349609375</v>
       </c>
       <c r="D317" t="n">
         <v>3</v>
@@ -4876,13 +4876,13 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B318" t="n">
         <v>0.9777777777777779</v>
       </c>
       <c r="C318" t="n">
-        <v>0.353515625</v>
+        <v>0.3483072916666667</v>
       </c>
       <c r="D318" t="n">
         <v>3</v>
@@ -4890,13 +4890,13 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B319" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C319" t="n">
-        <v>0.349609375</v>
+        <v>0.345703125</v>
       </c>
       <c r="D319" t="n">
         <v>3</v>
@@ -4904,13 +4904,13 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B320" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="C320" t="n">
-        <v>0.3483072916666667</v>
+        <v>0.3450520833333333</v>
       </c>
       <c r="D320" t="n">
         <v>3</v>
@@ -4918,13 +4918,13 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B321" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C321" t="n">
-        <v>0.345703125</v>
+        <v>0.33984375</v>
       </c>
       <c r="D321" t="n">
         <v>3</v>
@@ -4932,13 +4932,13 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B322" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C322" t="n">
-        <v>0.3450520833333333</v>
+        <v>0.337890625</v>
       </c>
       <c r="D322" t="n">
         <v>3</v>
@@ -4946,13 +4946,13 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B323" t="n">
         <v>0.9777777777777779</v>
       </c>
       <c r="C323" t="n">
-        <v>0.33984375</v>
+        <v>0.337890625</v>
       </c>
       <c r="D323" t="n">
         <v>3</v>
@@ -4960,13 +4960,13 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B324" t="n">
         <v>0.9555555555555556</v>
       </c>
       <c r="C324" t="n">
-        <v>0.337890625</v>
+        <v>0.3365885416666667</v>
       </c>
       <c r="D324" t="n">
         <v>3</v>
@@ -4974,13 +4974,13 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B325" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C325" t="n">
-        <v>0.337890625</v>
+        <v>0.3346354166666667</v>
       </c>
       <c r="D325" t="n">
         <v>3</v>
@@ -4988,13 +4988,13 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B326" t="n">
-        <v>0.9555555555555556</v>
+        <v>1</v>
       </c>
       <c r="C326" t="n">
-        <v>0.3365885416666667</v>
+        <v>0.3326822916666667</v>
       </c>
       <c r="D326" t="n">
         <v>3</v>
@@ -5002,13 +5002,13 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B327" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.7111111111111112</v>
       </c>
       <c r="C327" t="n">
-        <v>0.3346354166666667</v>
+        <v>0.3294270833333333</v>
       </c>
       <c r="D327" t="n">
         <v>3</v>
@@ -5016,13 +5016,13 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B328" t="n">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C328" t="n">
-        <v>0.3326822916666667</v>
+        <v>0.3255208333333333</v>
       </c>
       <c r="D328" t="n">
         <v>3</v>
@@ -5030,55 +5030,55 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B329" t="n">
-        <v>0.7111111111111112</v>
+        <v>1</v>
       </c>
       <c r="C329" t="n">
-        <v>0.3294270833333333</v>
+        <v>0.4140625</v>
       </c>
       <c r="D329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B330" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="C330" t="n">
-        <v>0.3255208333333333</v>
+        <v>0.3427734375</v>
       </c>
       <c r="D330" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B331" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C331" t="n">
-        <v>0.4140625</v>
+        <v>0.341796875</v>
       </c>
       <c r="D331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B332" t="n">
         <v>0.8</v>
       </c>
       <c r="C332" t="n">
-        <v>0.3427734375</v>
+        <v>0.337890625</v>
       </c>
       <c r="D332" t="n">
         <v>2</v>
@@ -5086,13 +5086,13 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B333" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C333" t="n">
-        <v>0.341796875</v>
+        <v>0.3525390625</v>
       </c>
       <c r="D333" t="n">
         <v>2</v>
@@ -5100,83 +5100,83 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B334" t="n">
-        <v>0.8</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="C334" t="n">
-        <v>0.337890625</v>
+        <v>0.31201171875</v>
       </c>
       <c r="D334" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B335" t="n">
-        <v>0.7</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C335" t="n">
-        <v>0.3525390625</v>
+        <v>0.390625</v>
       </c>
       <c r="D335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B336" t="n">
-        <v>0.5166666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="C336" t="n">
-        <v>0.31201171875</v>
+        <v>0.3330078125</v>
       </c>
       <c r="D336" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B337" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C337" t="n">
-        <v>0.390625</v>
+        <v>0.3092447916666667</v>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B338" t="n">
-        <v>0.7</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="C338" t="n">
-        <v>0.3330078125</v>
+        <v>0.3365885416666667</v>
       </c>
       <c r="D338" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B339" t="n">
         <v>0.7111111111111111</v>
       </c>
       <c r="C339" t="n">
-        <v>0.3092447916666667</v>
+        <v>0.2926432291666667</v>
       </c>
       <c r="D339" t="n">
         <v>3</v>
@@ -5184,13 +5184,13 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B340" t="n">
-        <v>0.5555555555555555</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="C340" t="n">
-        <v>0.3365885416666667</v>
+        <v>0.2958984375</v>
       </c>
       <c r="D340" t="n">
         <v>3</v>
@@ -5198,13 +5198,13 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B341" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C341" t="n">
-        <v>0.2926432291666667</v>
+        <v>0.2923177083333333</v>
       </c>
       <c r="D341" t="n">
         <v>3</v>
@@ -5212,13 +5212,13 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B342" t="n">
-        <v>0.688888888888889</v>
+        <v>0.6</v>
       </c>
       <c r="C342" t="n">
-        <v>0.2958984375</v>
+        <v>0.283203125</v>
       </c>
       <c r="D342" t="n">
         <v>3</v>
@@ -5226,13 +5226,13 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B343" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="C343" t="n">
-        <v>0.2923177083333333</v>
+        <v>0.2600911458333333</v>
       </c>
       <c r="D343" t="n">
         <v>3</v>
@@ -5240,43 +5240,15 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B344" t="n">
         <v>0.6</v>
       </c>
       <c r="C344" t="n">
-        <v>0.283203125</v>
+        <v>0.21875</v>
       </c>
       <c r="D344" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>367</v>
-      </c>
-      <c r="B345" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C345" t="n">
-        <v>0.2600911458333333</v>
-      </c>
-      <c r="D345" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>368</v>
-      </c>
-      <c r="B346" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C346" t="n">
-        <v>0.21875</v>
-      </c>
-      <c r="D346" t="n">
         <v>3</v>
       </c>
     </row>
